--- a/review/etnografiya/may-december/june/june.xlsx
+++ b/review/etnografiya/may-december/june/june.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли сделать упругую игрушку без резины?</t>
+          <t xml:space="preserve">Тряпичный мяч обходится без резины. Домашние материалы собираются в игрушку — игра начинается с умения придать форму тому, что под рукой.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему в народном календаре могли откладывать работу с землёй?</t>
+          <t xml:space="preserve">В народном представлении земля бывает именинницей. Отложенная работа в Духов день показывает обрядовую паузу внутри непрерывного сельского труда.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как июньский посев связан с зимней рубахой?</t>
+          <t xml:space="preserve">Имя Олёны-льняницы связывает посев с будущим полотном. Между летним полем и зимней рубахой лежит длинная цепь человеческой работы.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что важнее в этой игре — скорость или внимание?</t>
+          <t xml:space="preserve">В горелках пара разбегается, а водящему надо успеть отреагировать. Скорость работает вместе с вниманием к моменту начала движения.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда выгоднее бежать, а когда ждать?</t>
+          <t xml:space="preserve">В лапте удар открывает время для перебежки. Игрок соотносит свой старт с действиями соперников — командная игра требует общего расчёта.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как одна и та же пятёрка создаёт разные задачи?</t>
+          <t xml:space="preserve">Пять чурок складываются в разные фигуры городков. Материал остаётся прежним, но новое расположение меняет задачу для каждого броска.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем участники заранее договариваются о границах?</t>
+          <t xml:space="preserve">Граница площадки меняет игру в салочки. Договорённость участников становится действующим правилом, без которого один и тот же бег означает разное.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ритм помогает группе принять решение?</t>
+          <t xml:space="preserve">Считалка распределяет слоги между участниками и выбирает водящего. Ритм помогает группе начать игру с общего принятого порядка.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли игрушка сохранить подробности взрослого наряда?</t>
+          <t xml:space="preserve">Наряд самодельной куклы умещается в ладони. Игрушка способна сохранить детали взрослого местного костюма в масштабе детской игры.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как услышать момент для движения?</t>
+          <t xml:space="preserve">В Тимоне движение ног связано с наигрышем. Музыкальная опора становится телесным ритмом — услышанное продолжается в шаге танцующего.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как участники сохраняют общее движение?</t>
+          <t xml:space="preserve">Карагод держится на согласованном движении людей. Общий круг складывается из отдельных шагов, которые участники соотносят друг с другом.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Кто ведёт, а кто отвечает?</t>
+          <t xml:space="preserve">Инструменты плясового ансамбля вступают в разное время. В общем звучании слышны ведущие и ответные движения музыкальной фразы.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли рабочее дело иметь свой напев?</t>
+          <t xml:space="preserve">В Фощеватове песня сопровождает полотьё. Напев сохраняет связь с конкретным сезонным делом, а не только с праздничным выступлением.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему соседние песни звучат так по-разному?</t>
+          <t xml:space="preserve">В одном селе Лопатни живут песни разных слоёв репертуара. Соседство старого и нового показывает традицию, которая продолжает меняться.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где заканчивается строка, если мелодия ещё продолжается?</t>
+          <t xml:space="preserve">В песнях Осереди слово может закончиться раньше распева. Длинная музыкальная фраза раскрывает время, которое голос даёт одной строке.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ворот меняет усилие человека?</t>
+          <t xml:space="preserve">Рукоять колодезного ворота поднимает ведро из глубины. Поворот руки превращается в вертикальное движение тяжёлого запаса воды.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как распределить небольшой участок между разными культурами?</t>
+          <t xml:space="preserve">Огород рядом с домом делят между разными культурами. За небольшими грядами стоит сезонный порядок ухода и будущего семейного стола.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему старый рассказ о репке понятен через хозяйство?</t>
+          <t xml:space="preserve">Репа возвращает знакомую сказку в хозяйственный мир. За большой сказочной работой стоит настоящий овощ и его место в домашней еде.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что в летней еде нельзя повторить зимой без запасов?</t>
+          <t xml:space="preserve">Сезонная зелень меняет состав обеда. Щавель показывает, как стол связан с появлением свежих растений, а не только с зимним запасом.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что видно над водой и что происходит под ней?</t>
+          <t xml:space="preserve">Поплавок остаётся на поверхности и передаёт движение снасти. Маленькая вещь делает видимым то, что происходит под водой.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему названия дней хранят внимание к погоде?</t>
+          <t xml:space="preserve">Народный календарь сохраняет наблюдения за летней погодой. Имя Фёдора Стратилата становится точкой сезонной памяти, а не гарантией прогноза.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как плетёная ловушка удерживает добычу?</t>
+          <t xml:space="preserve">У мережи вход устроен иначе, чем выход. Форма рыболовной снасти направляет движение — результат зависит от конструкции целого предмета.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Зачем лодочнику сосуд, которым ничего не пьют?</t>
+          <t xml:space="preserve">Черпак убирает воду со дна лодки. Простая ручная вещь напоминает, что работа на воде включает постоянную заботу о самом судне.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Какая часть узора одновременно решает бытовую задачу?</t>
+          <t xml:space="preserve">Наличник украшает окно и закрывает стык. Красота резной детали соединена с устройством дома: узор занимает место конкретной строительной части.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как меняется дом, когда ставни закрывают?</t>
+          <t xml:space="preserve">Ставни дают окну дополнительное закрытие. Створки меняют вид фасада и повседневное обращение с границей между комнатой и улицей.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как отличить гречиху от привычного хлебного колоса?</t>
+          <t xml:space="preserve">Гречиха вошла в народное имя Акулинина дня. Календарное название связывает растение с сезонным вниманием людей к будущему урожаю.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему крупа не похожа на длинное зерно ржи?</t>
+          <t xml:space="preserve">У гречневого зерна характерная трёхгранная форма. Знакомая крупа возвращает взгляд от тарелки к растению и обработке урожая.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как цветы удерживают композицию на круглом подносе?</t>
+          <t xml:space="preserve">Листья жостовской росписи собираются веерными движениями кисти. Растительный мотив держится на порядке мазков, а не на обводке готового контура.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как узнать игрушку ещё до раскраски?</t>
+          <t xml:space="preserve">Филимоновская свистулька вытягивает силуэт в глине. Местный почерк виден ещё до росписи — форму и звучание мастер создаёт вместе.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что человек выбирает рассказать близким прежде всего?</t>
+          <t xml:space="preserve">Летние новости укладываются на одном листе. Домашнее письмо сохраняет личный голос человека, которому предстояло преодолеть расстояние словами.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
